--- a/content/기록문화_중등_콘텐츠.xlsx
+++ b/content/기록문화_중등_콘텐츠.xlsx
@@ -503,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -811,6 +811,18 @@
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>이미지: images/에 같은 파일명으로 교체 → 커밋. 게임은 no로 참조하므로 코드수정 불필요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>connection</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>기록관리 연결설명</t>
         </is>
       </c>
     </row>
@@ -1823,7 +1835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I85"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1884,6 +1896,11 @@
           <t>content</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>connection</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">

--- a/content/기록문화_중등_콘텐츠.xlsx
+++ b/content/기록문화_중등_콘텐츠.xlsx
@@ -1983,6 +1983,11 @@
           <t>대장경판은 산벚나무·돌배나무 같은 단단한 나무를 바닷물에 담그고 소금물에 삶은 뒤 그늘에서 말려 뒤틀림과 갈라짐을 막았다. 이렇게 가공한 목판 81,258장에 약 5,200만 자를 한 자 한 자 새겼으며, 글자체와 새김의 깊이가 거의 균일하여 통일된 모양을 유지하고 있다. 새긴 뒤에는 옻칠을 하고 네 모서리에 구리판을 붙여 휘어짐을 막았으며, 강화도 대장도감과 분사도감에서 승려와 장인들이 분업하여 협업하였다.</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>기록은 만들 때의 정확성이 곧 신뢰의 바탕이 된다. 대장경판 5,200만 자에 오탈자가 거의 없도록 교정에 공을 들인 것처럼, 오늘날 기록관리에서도 내용이 사실과 어긋나지 않게 하는 '무결성(無缺性)'을 가장 중요한 원칙으로 삼는다.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -2026,6 +2031,11 @@
           <t>완성된 대장경판은 강화도 선원사에 봉안되었다가 1398년경 합천 해인사로 옮겨져 오늘날까지 보관되고 있다. 해인사 장경판전은 자연 통풍과 습도 조절이 가능하도록 설계되어 770여 년 동안 목판을 안전하게 지켜 왔다. 한국전쟁 당시 김영환 대령이 가야산 일대 폭격 명령을 거부하여 대장경판이 피해를 입지 않았으며, 이 사실은 합천 해인사와 국가유산청 자료에 소개되어 있다.</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>기록을 오래 남기려면 무엇을 남기느냐만큼 어디에, 어떤 환경에 두느냐가 중요하다. 장경판전이 통풍과 습도를 자연적으로 조절하도록 설계된 것은, 온도·습도를 일정하게 유지하는 오늘날의 '보존 환경 관리'와 같은 원리다.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -2069,6 +2079,11 @@
           <t>해인사 대장경판은 현존하는 한역 대장경 가운데 가장 완전하고 정확한 판본으로 평가받으며, 동아시아 불교 경전 연구의 표준이 되고 있다. 81,258장의 방대한 분량에도 오탈자가 거의 없어 고려 인쇄·출판 기술의 정점을 보여 주며, 호국 불교 사상과 국가적 출판 사업이 결합된 역사적 의미도 크다. 보관 건물인 장경판전은 1995년, 대장경판은 2007년 유네스코에 각각 등재되었다.</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>모든 기록을 영원히 남길 수는 없기에, '이 기록이 왜 중요한가'를 따져 보존할 가치를 가려내는 일이 필요하다. 이러한 '평가·선별'은 기록 전문가(아키비스트)의 핵심 업무이며, 세계기록유산 등재 역시 그 가치를 공식적으로 인정받는 과정이다.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -2229,6 +2244,11 @@
           <t>직지는 밀랍에 글자 모양을 새겨 거푸집을 만든 뒤 녹인 쇳물을 부어 활자를 찍어 내는 밀랍주조법으로 제작되었다. 글자 하나하나를 금속으로 미리 만든 뒤 판에 짜 맞추어 종이에 찍어 내는 금속활자 인쇄 방식이다. 원래 상·하 두 권으로 간행되었으나 현재는 하권 1책만이 전한다. 1455년경 독일 구텐베르크의 금속활자 성경보다 약 78년 앞선 것으로, 현존하는 세계 최고(最古)의 금속활자 인쇄본으로 인정받고 있다.</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>기록을 남기는 기술은 시대에 따라 진화해 왔다. 금속활자는 같은 내용을 똑같이 여러 부 찍어낼 수 있어 기록의 '복제'와 '확산'을 가능하게 한 결정적 전환점이었다. 복본을 만들어 널리 퍼뜨리는 것은 기록을 잃지 않고 공유하는 가장 효과적인 방법이다.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -2468,6 +2488,11 @@
           <t>실록의 바탕은 사관(史官)이 작성한 사초(史草)와 각 관청의 시정기·승정원일기 등 공식 기록이었다. 사관은 임금의 말과 행동, 정사의 득실을 직필하였고, 임금조차 사초를 볼 수 없도록 하여 객관성을 지켰다. 선왕이 세상을 떠나면 실록청을 설치해 초초·중초·정초의 세 단계를 거쳐 실록을 완성하였으며, 편찬 후에는 사용한 사초를 물에 씻어 내는 세초(洗草)로 기록의 비밀을 지켰다.</t>
         </is>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>기록하는 사람이 어떤 권력의 압력에도 사실을 고쳐 쓰지 않는 것은 예나 지금이나 변하지 않는 원칙이다. 임금조차 사초를 볼 수 없게 한 사관의 독립성은, 기록의 객관성과 '진본성(authenticity)'을 지키는 제도적 장치였다.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -2511,6 +2536,11 @@
           <t>조선왕조실록은 화재와 전란에 대비해 한양 춘추관과 충주·성주·전주의 4대 사고에 나누어 보관되었다. 1592년 임진왜란 때 전주 사고를 제외한 세 곳이 불탔으나, 선비 안의·손홍록이 전주본을 정읍 내장산으로 옮겨 지켰다. 전쟁 후 조선 정부는 이를 토대로 다시 인쇄하여 강화도 마니산·봉화 태백산·영변 묘향산·평창 오대산·한양 춘추관에 분산 보관하였고, 이 덕분에 일제강점기와 한국전쟁의 혼란 속에서도 실록이 오늘까지 전해질 수 있었다.</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>중요한 기록을 한곳에만 두면 화재나 전란 한 번으로 영원히 사라질 수 있다. 실록을 여러 사고(史庫)에 나누어 둔 것은 오늘날에도 핵심 원칙인 '분산 보존'이며, 디지털 시대에는 데이터를 여러 곳에 백업하는 방식으로 이어진다.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -2554,6 +2584,11 @@
           <t>한 왕조가 472년간 이어진 통치 과정을 거의 빠짐없이 기록한 사례는 세계적으로 유례를 찾기 힘들며, 분량과 시간적 연속성에서 비교 대상이 없다. 정치·외교뿐 아니라 천재지변·사회·풍속·과학기술까지 폭넓게 담아 조선 사회 전반을 이해하는 핵심 사료로 활용된다. 다만 당쟁기에 집권당에 유리하게 편찬된 경우도 있어 비판적으로 읽을 필요가 있다. 1973년 국보로 지정되었고, 1997년 유네스코 세계기록유산에 등재되었다.</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>기록의 가치는 빈틈없이 이어진 '완전성'과 '연속성'에서 높아진다. 472년을 끊김 없이 기록한 실록처럼, 시간의 공백이 적은 기록일수록 그 시대를 온전히 증언할 수 있다.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -2636,6 +2671,11 @@
           <t>조선왕조실록은 국사편찬위원회가 운영하는 '조선왕조실록' 사이트에서 한문 원문과 한글 번역, 영인 이미지까지 누구나 무료로 검색·열람할 수 있다. 강원도 평창의 국립조선왕조실록박물관에서는 환수된 오대산사고본 원본과 사고 운영·편찬 과정을 보여 주는 상설 전시를 관람할 수 있으며, 실록 원본을 상시로 직접 볼 수 있는 유일한 곳이다. 다만 보존을 위해 대부분 기관에서 원본의 상시 공개는 제한되며, 관람은 주로 디지털 자료와 복제본을 통해 이루어진다.</t>
         </is>
       </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>원본은 손상되지 않게 보호하면서 그 내용은 누구나 자유롭게 이용하게 하는 것이 기록 서비스의 이상이다. 원본 대신 디지털 이미지와 번역본을 공개하는 방식은 '보존'과 '활용'이라는 두 목표를 동시에 이루는 길이다.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -2757,6 +2797,11 @@
           <t xml:space="preserve">해례본은 조선 시대에 인쇄되었으나 전란을 거치며 거의 사라져 오랫동안 실물이 전하지 않는 책으로 여겨졌다. 1940년 경상북도 안동의 한 고가에서 해례본 한 책이 발견되어 학계에 알려졌고, 수집가 간송 전형필이 이를 매입하여 일제강점기와 한국전쟁 속에서도 안전하게 지켜 냈다. 이 책이 '간송본'이다. 2008년에는 경상북도 상주에서 또 다른 해례본이 발견되어 '상주본'이라 불린다. </t>
         </is>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>단 한 부만 남은 기록은 잃는 순간 영원히 복구할 수 없다. 그래서 기록관리에서는 중요한 자료일수록 복본을 만들어 여러 곳에 나누어 두는 것을 원칙으로 삼는다. 해례본이 우연한 발견과 한 수집가의 노력으로 겨우 전해진 사실은, 복본과 분산 보존이 왜 필요한지를 역설적으로 보여 준다.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -2800,6 +2845,11 @@
           <t>해례본은 세계 문자 가운데 매우 드물게 글자를 만든 사람과 시기, 그리고 그 원리가 함께 기록된 책으로, 한글이 독자적이고 과학적인 설계의 산물임을 직접 증명한다. 1962년 국보로 지정되었고, 1997년 조선왕조실록과 함께 유네스코 세계기록유산에 등재되었다. 한국 정부는 해례본에 적힌 반포일을 기준으로 10월 9일을 한글날 국경일로 지정하여 그 가치를 기리고 있다.</t>
         </is>
       </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>세상에 하나뿐인 기록은 대체할 수 없다는 점에서 그 자체로 막대한 가치를 지닌다. 만든 사람·시기·원리가 함께 담긴 해례본처럼, 기록의 희소성과 고유성을 가려 가치를 매기는 일 또한 기록 전문가의 중요한 역할이다.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -3078,6 +3128,11 @@
           <t>이순신의 친필 초고 7책은 현재 충남 아산 현충사 안에 자리한 충무공이순신기념관 수장고에 있다. 국가유산청 현충사관리소가 관리를 맡고 있으며, 감압 훈증·결실부 보강·오동나무 상자 제작 등의 방식으로 유물 상태를 유지하고 있다. 기념관에는 난중일기 외에도 국보 9점·보물 20점을 포함한 991점의 유물이 함께 소장되어 있다. 원문 사진과 텍스트는 국가기록유산 누리집에서 누구나 검색·열람할 수 있다.</t>
         </is>
       </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>오래된 종이 기록은 온도와 습도에 매우 민감해, 너무 덥거나 습하면 곰팡이가 슬고 바스러진다. 항온·항습 수장고에서 환경을 일정하게 유지하고 훈증으로 해충과 곰팡이를 막는 일은, 종이 기록을 지키는 기본적인 보존 처리다.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -3199,6 +3254,11 @@
           <t>허준이 책임자가 되어 양예수·이명원·김응탁·정예남·정작 등과 편찬을 시작하였으나 정유재란으로 중단되었고, 이후 허준이 단독으로 완성하였다. 책은 내경편·외형편·잡병편·탕액편·침구편의 5편으로 구성되어 몸의 안팎, 병의 원인과 치료법, 약재, 침과 뜸을 종합 정리하였다.  중국 한나라에서 명나라에 이르는 200여 종의 문헌과 조선 의서를 참고하였으며, 약재 이름에 조선 사람이 부르는 이름을 한글로 함께 적어 누구나 약재를 찾을 수 있게 하였다.</t>
         </is>
       </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>기록은 그것을 읽을 사람이 이해할 수 있어야 제 역할을 한다. 허준이 약재 이름에 한글을 함께 적은 것은 전문 지식의 '접근성'을 높인 셈이다. 어려운 정보를 누구나 찾아 쓸 수 있게 정리하는 것도 좋은 기록의 조건이다.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -3359,6 +3419,11 @@
           <t>동의보감은 한국고전번역원 한국고전종합DB와 한국한의학연구원 한의학고전DB에서 한문 원문과 한글 번역을 누구나 무료로 검색·열람할 수 있다. 서울 강서구 허준박물관에서는 허준의 생애와 동의보감 편찬 과정을 보여 주는 상설 전시와 교육 프로그램이 운영된다. 다만 보존을 위해 초간본 원본의 직접 열람은 엄격히 제한된다.</t>
         </is>
       </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>기록을 디지털화해 인터넷으로 제공하면, 멀리 있는 사람도 원본을 훼손하지 않고 내용을 볼 수 있다. 이러한 '디지털 아카이빙'과 온라인 서비스는 기록의 보존과 공개를 동시에 넓히는 오늘날 기록관리의 핵심 흐름이다.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -3441,6 +3506,11 @@
           <t>국채보상운동 기록물은 전국 각지에서 자발적으로 일어난 운동의 성격상 국가가 한꺼번에 만든 자료가 아니다. 『대한매일신보』, 『황성신문』, 『제국신문』, 『만세보』 등 당시 신문은 의연금을 낸 사람들의 이름과 금액을 매일 보도하여 공개 회계 역할을 하였고, 이 지면 자체가 핵심 기록이 되었다. 또한 부녀층이 각종 패물을 의연소에 보내는 등 각계각층이 참여하면서 취지문, 영수증, 편지 등 다양한 형태의 민간 기록물이 동시다발적으로 남겨졌다.</t>
         </is>
       </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>하나의 사건도 여러 종류의 기록이 함께 있으면 훨씬 정확하게 재구성할 수 있다. 명단·영수증·신문 기사가 서로를 뒷받침하듯, 출처가 다른 기록을 견주어 사실을 확인하는 '교차 검증'은 진실에 다가가는 기본 방법이다.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -3484,6 +3554,11 @@
           <t>일제 통감부는 1908년 베델과 양기탁의 '국채보상금 횡령 사건'을 조작해 운동을 와해시켰다. 그러나 『대한매일신보』 등 언론 보도와 개인이 소장한 취지문·기부영수증 덕분에 핵심 기록이 살아남았다. 이후 2002년 창립된 국채보상운동기념사업회와 대구시가 흩어진 자료를 수집하여 유네스코에 등재된 2,475건의 기록물을 갖추게 되었다.</t>
         </is>
       </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>권력이 특정 기록을 없애려 해도, 여러 곳에 흩어져 있으면 완전히 지울 수 없다. 일제의 탄압에도 신문과 개인 소장 자료 덕분에 기록이 살아남은 것은, 분산 보존이 기록을 지키는 강력한 방패임을 보여 준다.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
@@ -3527,6 +3602,11 @@
           <t>국채보상운동 기록물은 국가 위기 시 시민들이 자발적으로 나서 외채 상환을 시도한 세계사적으로 유례가 없는 시민 주도 모금 운동의 과정을 담고 있다. 신분·성별·직업을 초월한 각계각층의 참여, 신문을 통한 투명한 공개 회계가 두드러지며, 이 정신은 1997년 IMF 경제위기 당시 '금 모으기 운동'으로 이어지는 한국 시민운동의 원형으로 평가된다. 2017년 유네스코 세계기록유산에 등재되었다.</t>
         </is>
       </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>정부가 만든 공식 문서만으로는 한 시대를 온전히 알 수 없다. 평범한 사람들이 남긴 취지문·영수증·편지 같은 민간 기록은 공식 기록의 빈자리를 채워, 역사를 더 입체적으로 증언한다.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
@@ -3687,6 +3767,11 @@
           <t>사건이 벌어지던 당시 군·경·미군정·법원은 작전 보고서와 군법회의 재판 기록을 각자 남겼고, 신문사와 기자들도 현장을 사진과 기사로 기록했다. 세월이 흐른 뒤에는 살아남은 피해자와 유족, 목격자들의 증언이 영상·녹음·문서로 정리되었다. 2003년 정부 공식 진상조사보고서가 더해지면서, 문서·엽서·비디오·오디오를 아우르는 총 1만 4,673건의 기록물이 완성되었다.</t>
         </is>
       </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>한쪽의 기록만 남으면 사건은 일방적으로 그려질 수 있다. 군·경·법원의 문서와 피해자·목격자의 증언이 함께 보존되어야 여러 시각에서 비교해 진실에 가까이 갈 수 있다. 서로 다른 출처를 두루 모으는 것이 균형 잡힌 기록의 출발점이다.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -3730,6 +3815,11 @@
           <t>4·3은 오랫동안 반공법·국가보안법 아래 입에 올리기조차 어려운 금기였고, 피해자와 유족도 사건을 드러낼 수 없었다. 1987년 민주화 이후 학생·시민사회·유족회가 본격적으로 진상 규명 운동에 나섰고, 마침내 2000년 4·3특별법이 제정되면서 기록 수집과 구술 채록이 공식적으로 시작됐다. 2003년 정부 공식 진상조사보고서가 확정되고 대통령이 사과하면서, 흩어졌던 기록들이 체계적으로 모이기 시작했다.</t>
         </is>
       </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>기록이 금기로 묻히면 진실도 함께 묻힌다. 4·3이 오랫동안 말할 수 없는 사건이었다가 진상 규명과 함께 기록이 모이기 시작한 과정은, 기록을 지키고 공개하는 일이 곧 진실을 밝히는 길임을 보여 준다.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -3773,6 +3863,11 @@
           <t>분단 직후 한반도에서 일어난 대규모 민간인 희생의 진실이 국가와 시민사회의 노력으로 밝혀지는 전 과정을 담았다는 점에서 제주4·3 기록물은 세계적으로 희귀한 자료다. 가해 기관의 문서, 외국 자료, 피해자 구술이 함께 보존되어 다양한 시각으로 검증이 가능하며, 공식 사과·명예 회복·화해와 상생으로 이어진 과거사 해결의 방향성을 전 세계에 제시한다. 2025년 유네스코 세계기록유산에 등재되었다.</t>
         </is>
       </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>기쁜 역사뿐 아니라 아픈 역사의 기록도 소중히 보존해야 한다. 비극의 진실과 그 해결 과정을 기록으로 남기는 것은, 같은 잘못을 되풀이하지 않기 위한 사회의 약속이자 기록이 지닌 힘이다.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
@@ -3816,6 +3911,11 @@
           <t>4·3 관련 기록물은 제주시 명림로에 자리한 제주4·3평화기념관이 핵심 기관으로서 기록·보존·연구를 담당하며, 국가기록원 등 정부 기관에 이관된 자료도 함께 관리되고 있다. 제주4·3평화재단은 4·3아카이브를 통해 디지털 자료를 온라인으로 제공하고 있으며, 피해자·목격자의 구술 채록과 추가 진상조사 사업이 현재도 이어지고 있다.</t>
         </is>
       </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>문서에 적히지 않은 경험은 사람의 기억 속에만 남아 있다. 피해자와 목격자의 증언을 영상·음성으로 채록하는 '구술 기록(oral history)'은, 공식 문서의 공백을 메우는 중요한 보존 방법이다.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
@@ -3937,6 +4037,11 @@
           <t>4·19혁명 기록물은 학생·시민·언론·정부 등 다양한 주체가 생산한 자료의 집합이다. 학생과 시민들은 선언문과 결의문을 만들어 배포하였고, 기자와 시민 사진가들은 현장 사진과 영상을 남겼다. 국가기관·국회·정당은 시위 대응 및 수습 보고서를 작성하였으며, 이승만 하야·허정 과도내각 수립 과정에서도 정권 교체 관련 문서가 생산되었다. 현재 등재된 기록물은 총 1,019점이다.</t>
         </is>
       </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>사건이 벌어지는 바로 그 순간에 생산된 기록을 '1차 사료'라 한다. 현장의 선언문·사진·영상은 시간이 지나 재구성한 회고보다 훨씬 정확해, 역사 연구에서 가장 신뢰받는 자료가 된다.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
@@ -4019,6 +4124,11 @@
           <t>4·19혁명 기록물은 학생과 시민이 부정 선거에 맞서 정부를 교체시킨 1960년 시민 혁명의 전 과정을 1차 자료로 보여 준다. 이 기록은 한국 민주주의의 출발점이자 이후 5·18민주화운동과 6월 항쟁 등으로 이어지는 시민운동의 원형이 된 사건의 실상을 입체적으로 알려 준다. 그 결과 한국 사회에서 ‘민주주의는 시민이 만든다’는 의식이 자리 잡는 데 결정적인 역할을 하였다. 이러한 가치를 인정받아 4·19혁명 기록물은 2023년 유네스코 세계기록유산에 등재되었다.</t>
         </is>
       </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>그 시대를 살아간 사람들이 직접 남긴 기록은 무엇보다 생생한 증언이 된다. 학생과 시민이 만든 4·19 기록은 당대의 목소리를 오늘에 전하며, 기록이 한 사회의 기억을 잇는 매개임을 보여 준다.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
@@ -4062,6 +4172,11 @@
           <t>4·19혁명 기록물은 한 곳이 아니라 여러 기관에 분산되어 보관되고 있다. 서울의 4·19혁명기념도서관과 인근의 국립4·19민주묘지가 핵심 기관 역할을 하며, 사진·문서·신문·영상·구술 자료를 종합적으로 관리한다. 행정안전부 국가기록원과 국립중앙도서관, 대학·언론사 자료실 등에도 관련 문서와 보도 자료가 다수 소장되어 있다. 보존 시설은 항온·항습 수장고를 갖추고 있으며, 자료의 산화·열화를 막기 위해 정기 점검과 디지털화 작업을 병행하고 있다.</t>
         </is>
       </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>오래된 종이·필름은 시간이 지날수록 바래고 부서진다. 이를 디지털로 변환해 두면 원본의 손상을 막으면서 더 많은 사람이 안전하게 이용할 수 있어, 디지털화는 보존과 활용을 함께 잡는 방법이다.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
@@ -4261,6 +4376,11 @@
           <t>한국의 산림녹화는 전쟁으로 황폐해진 국토를 한 세대 만에 푸른 숲으로 복원한 세계적으로 보기 드문 성공 사례로 꼽힌다. 정부의 치밀한 정책 기획과 행정적 실행, 그리고 국민의 자발적 참여가 어떻게 맞물려 기적을 이뤄냈는지 전 과정을 입체적으로 보여준다. 이 기록과 경험은 현재 여러 개발도상국의 산림 복원 사업에 훌륭한 길잡이로 활용되고 있다. 이러한 인류 보편적 가치와 역사적 중요성을 인정받아 2025년 유네스코 세계기록유산에 최종 등재되었다.</t>
         </is>
       </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>성공한 경험을 체계적으로 기록해 두면, 다른 곳에서도 그 과정을 배워 되풀이할 수 있다. 황폐한 국토를 숲으로 되살린 정책과 실행의 기록이 여러 개발도상국의 길잡이가 되듯, 기록은 미래 세대와 다른 사회를 위한 자산이 된다.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
@@ -4421,6 +4541,11 @@
           <t>기록물은 다양한 주체에 의해 만들어졌다. 시민과 학생들은 성명서, 선언문, 일기를 남겼고, 외국 기자와 사진가들은 현장 사진과 영상을 촬영하고 취재수첩, 메모 등을 남겼다. 계엄군과 정부의 작전 보고서, 군사법기관 재판자료, 수사기록 등 행정·사법 자료도 다량 생산되었다. 이후 피해자와 유가족의 방대한 구술 증언이 수집·정리되었고, 1995년 5·18특별법 제정 이후 국회와 정부 차원의 진상조사 자료도 함께 추가되었다.</t>
         </is>
       </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>한 사건을 여러 주체가 서로 다른 방식으로 기록하면 더 완전한 전모가 드러난다. 시민의 일기, 외신 기자의 사진, 군과 정부의 문서가 함께 남은 것처럼, 다양한 출처의 기록을 모으는 '다원적 기록'은 사건을 입체적으로 증언한다.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
@@ -4464,6 +4589,11 @@
           <t>항쟁 직후 신군부 정권은 사건의 진상을  폭동으로 왜곡하여 5·18에 대한 침묵을 강요했다. 그러나 1980년대 중반부터 진실을 알리려는 각계각층의 노력이 이어졌고, 1988년 국회 광주특위 청문회 개최로 진상 규명이 본격화되었다. 1995년 5·18특별법 제정 이후 정부 차원의 자료 수집이 가속화되었으며, 5·18기념재단·전남대 5·18연구소·국사편찬위원회 등이 사진·영상·증언을 체계적으로 수집·보존하였다.</t>
         </is>
       </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>기록을 지우려는 힘과 지키려는 힘이 맞설 때, 끝내 살아남은 기록이 진실을 증언한다. 왜곡과 침묵의 강요 속에서도 시민과 연구기관이 자료를 모아 지켜 낸 5·18 기록은, 기록이 결국 진실의 편에 선다는 사실을 보여 준다.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
@@ -4507,6 +4637,11 @@
           <t>5·18민주화운동 기록물은 국가 폭력에 맞선 시민의 저항부터 진상 규명과 피해 보상까지 전 과정을 담은 종합 기록이다. 시민·언론·정부·군·국제 사회의 자료가 함께 보존되어 한 사건을 다양한 시각에서 비교·검증할 수 있다. 유네스코는 이 기록물이 아시아 여러 나라의 민주화 운동에 영향을 주었음을 등재 사유로 명시하며, 한국 민주주의의 분기점이 된 사건의 1차 자료이자 국제 인권 운동의 비교 자료로서 가치를 지닌다.</t>
         </is>
       </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>어떤 기록은 한 나라의 사건을 넘어 인류 공통의 교훈이 된다. 5·18 기록이 아시아 여러 나라의 민주화 운동에 영향을 준 점이 등재 사유가 되었듯, 보편적 가치를 지닌 기록은 국경을 넘어 공유되는 인류의 유산이 된다.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
@@ -4550,6 +4685,11 @@
           <t>5·18 관련 기록물은 광주시에 있는  5·18민주화운동기록관이 핵심 기관으로서 3개의 수장고와 보존처리실을 갖추어 문서·사진·영상·구술 자료를 보존하고 있다. 기록물은 5·18기념재단·전남대5·18연구소·천주교광주대교구 정의평화위원회·국사편찬위원회·국가기록원 등에 분산 보존되어 있으며, 피해자·목격자의 구술 채록 사업이 지속되고 있다.</t>
         </is>
       </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>증언할 수 있는 사람이 살아 있을 때 기록하지 않으면, 그 기억은 시간이 지나 영원히 사라진다. 그래서 피해자·목격자의 구술 채록은 한시가 급한 작업이며, 5·18기록관 등은 지금도 이 일을 이어 가고 있다.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
@@ -4671,6 +4811,11 @@
           <t>이 기록물의 뼈대는 138일의 생방송을 모두 담아낸 463개의 비디오테이프다. 화면 속에는 혈육을 찾는 애타는 호소와 극적인 상봉 장면이 고스란히 남아 있다. 여기에 이산가족이 직접 쓴 사연 신청서, 제작진의 큐시트와 수첩, 보도 자료 등 2만여 건의 방대한 종이 문서가 포함되어있다. 이는 텔레비전이라는 대중 매체가 어떻게 거대한 사회적 현상을 이끌어내고 그 전 과정을 낱낱이 기록했는지 입체적으로 보여주는 매우 독특한 복합 매체 사료다.</t>
         </is>
       </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>기록은 종이에만 담기지 않는다. 비디오테이프·사진·음성처럼 기록의 매체는 시대에 따라 달라지며, 형태가 다른 자료가 모인 '복합 매체 기록'은 사건을 더 생생하게 전한다. 매체가 무엇이든 보존할 가치가 있다는 점은 변하지 않는다.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
@@ -4753,6 +4898,11 @@
           <t>이 기록물은 텔레비전이라는 대중 매체가 분단의 아픔을 치유하고 대규모 가족 재회를 이루어낸 세계적으로 희귀한 역사적 증거다. 138일의 생방송, 10만 명이 넘는 신청과 1만여 건의 상봉 실적은 한국전쟁이 남긴 흉터를 여실히 보여준다. 이 방송의 거대한 파급력은 이후 남북 이산가족 상봉 논의를 이끌어내는 핵심적인 마중물 역할을 수행했다. 전쟁의 비극을 평화로 승화시킨 보편적 가치를 인정받아 2015년 유네스코 세계기록유산에 등재되었다.</t>
         </is>
       </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>기록은 사실뿐 아니라 그 시대 사람들의 아픔과 기쁨까지 담아낸다. 이산가족이 다시 만나는 장면이 오늘날까지 깊은 울림을 주는 것은, 기록이 단순한 정보를 넘어 공동체의 감정과 기억을 잇는 힘을 지니기 때문이다.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
@@ -4911,6 +5061,11 @@
           <t>승정원의 전담 기록관인 주서와 가주서가 매일 작성했다. 날씨부터 왕의 동선, 어전 회의의 생생한 대화, 신하들이 올린 상소문까지 국정 전반을 시간순으로 꼼꼼히 적었다. 이렇게 작성된 일기는 보통 한 달 단위로 묶여 보관되며 훗날 실록 편찬의 핵심 기초 자료로 쓰였다. 방대한 분업 시스템과 철저한 업무 규정 덕분에 글자 수만 무려 2억 4천만 자에 달하는 세계 최대 규모의 단일 사료가 탄생할 수 있었다.</t>
         </is>
       </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>매일 정해진 담당자가 정해진 규칙에 따라 빠짐없이 기록하는 '체계적인 기록 시스템'이 있었기에, 2억 4천만 자에 이르는 방대한 일기가 일관되게 완성될 수 있었다. 누가·언제·무엇을 기록할지 정한 규정과 분업은, 오늘날 조직이 업무를 빠짐없이 남기는 '기록 관리 체계'와 같은 원리다.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="9" t="n">
@@ -4952,6 +5107,11 @@
           <t xml:space="preserve">잦은 전란과 화재는 기록 보존의 가장 큰 위기였다. 임진왜란과 1624년 이괄의 난으로 막대한 분량이 재가 되었고, 1744년 대화재 때도 큰 손실을 입었다. 하지만 조선 정부는 일기청을 따로 꾸려 불탄 기록을 다시 복구하는 엄청난 집념을 보였다. 원본은 일제강점기를 거쳐 현재 서울대학교 규장각으로 오게 되었다. </t>
         </is>
       </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>기록은 만드는 것만큼 지키고 되살리는 일이 어렵다. 전란과 화재로 일기가 거듭 불탔지만 조선이 일기청을 세워 불탄 부분을 복구한 것은, 손상된 기록을 포기하지 않고 되살리는 '복원' 작업에 해당한다. 이러한 집념이 방대한 사료를 오늘에 전했다.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="9" t="n">
@@ -5151,6 +5311,11 @@
           <t>행사가 결정되면 국가는 도감(都監)이라는 임시 기구를 설치해 준비부터 마무리까지 전 과정을 주관하게 하였다. 도감은 행사를 마친 뒤 비용·물품·참여 관원과 장인 명단·의식 절차 등을 정리해 의궤를 편찬하였고, 핵심 장면은 화원이 반차도(班次圖) 같은 채색 그림으로 그려 넣었다. 의궤는 임금이 직접 보는 어람용(御覽用)과 분상용(分上用)으로 나뉘어 5~9부가 제작되었으며, 어람용은 비단 표지와 고급 종이로 정성껏 만들어졌다.</t>
         </is>
       </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>의궤는 행사의 모든 과정을 글과 그림으로 상세히 남겨 훗날 그대로 재현할 수 있을 만큼 정밀한 '업무 기록'이다. 비용·물품·참여자·절차까지 빠짐없이 적고 여러 부를 만들어 나눈 방식은, 일의 전 과정을 투명하게 남기고 복본으로 보존하는 오늘날의 기록관리 원칙과 맞닿아 있다.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="9" t="n">
@@ -5190,6 +5355,11 @@
       <c r="I82" s="10" t="inlineStr">
         <is>
           <t>의궤는 봉화 태백산, 무주 적상산, 평창 오대산, 강화도 정족산 등 여러 사고에 나누어 보관되어 변란에 대비하였다. 그러나 1866년 병인양요 때 프랑스 군대가 강화도 외규장각을 방화하면서 의궤를 포함한 340여 도서를 약탈하였다. 약탈된 의궤는 프랑스 국립도서관에 방치되다가 1979년 박병선에 의해 발견되었고, 2011년 5년마다 갱신하는 대여 방식으로 국립중앙박물관에 돌아왔다.</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>의궤를 여러 사고에 나누어 둔 것은 변란에 대비한 '분산 보존'이었다. 한편 외규장각 의궤가 약탈되었다가 한 연구자의 노력으로 발견되어 돌아온 과정은, 빼앗긴 기록을 되찾는 '기록 환수'가 한 나라의 역사 주권과 직결됨을 보여 준다.</t>
         </is>
       </c>
     </row>

--- a/content/기록문화_중등_콘텐츠.xlsx
+++ b/content/기록문화_중등_콘텐츠.xlsx
@@ -5354,7 +5354,7 @@
       </c>
       <c r="I82" s="10" t="inlineStr">
         <is>
-          <t>의궤는 봉화 태백산, 무주 적상산, 평창 오대산, 강화도 정족산 등 여러 사고에 나누어 보관되어 변란에 대비하였다. 그러나 1866년 병인양요 때 프랑스 군대가 강화도 외규장각을 방화하면서 의궤를 포함한 340여 도서를 약탈하였다. 약탈된 의궤는 프랑스 국립도서관에 방치되다가 1979년 박병선에 의해 발견되었고, 2011년 5년마다 갱신하는 대여 방식으로 국립중앙박물관에 돌아왔다.</t>
+          <t>의궤는 봉화 태백산, 무주 적상산, 평창 오대산, 강화도 정족산 등 여러 사고에 나누어 보관되어 변란에 대비하였다. 그러나 1866년 병인양요 때 프랑스 군대가 강화도 외규장각을 방화하면서 의궤를 포함한 340여 도서를 약탈하였다. 약탈된 의궤는 프랑스 국립도서관에 방치되다가 1975년 박병선에 의해 발견되었고, 2011년 5년마다 갱신하는 대여 방식으로 국립중앙박물관에 돌아왔다.</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">

--- a/content/기록문화_중등_콘텐츠.xlsx
+++ b/content/기록문화_중등_콘텐츠.xlsx
@@ -10,6 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="items" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="content" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="levels" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="badges" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sections" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5485,4 +5488,418 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>icon</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>기록 루키</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>level1.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>기록 헌터</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>level2.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>기록 레인저</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>level3.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>9</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>기록 가디언</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>level4.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>12</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>기록 마스터</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>level5.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>14</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>기록 레전드</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>level6.png</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>emoji</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>고려</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>🏛️</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>고려 기록 전문가</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>고려 시대의 모든 기록 유산을 완료했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>조선</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>📜</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>조선 기록 전문가</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>조선 시대의 모든 기록 유산을 완료했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>근현대</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>📷</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>근현대 기록 전문가</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>근현대의 모든 기록 유산을 완료했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>🏆</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>한국 기록 수호자</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>모든 시대의 기록 유산을 완료했습니다! 당신은 진정한 기록 수호자입니다.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>sub</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>생산 배경</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>이 기록은 왜 만들어졌는가?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>생산 방법</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>누가, 어떻게 만들었는가?</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>생존 이야기</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>어떻게 현재까지 남게 되었는가?</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>기록문화적 가치</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>왜 이 기록이 중요한가?</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>현재 보존 방법</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>지금은 어떻게 보존되고 있는가?</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>접근·열람 방법</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>일반인이 이 기록을 보려면?</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/content/기록문화_중등_콘텐츠.xlsx
+++ b/content/기록문화_중등_콘텐츠.xlsx
@@ -5640,7 +5640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5669,6 +5669,11 @@
           <t>desc</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>icon</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5688,12 +5693,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>고려 기록 전문가</t>
+          <t>고려 컬렉터</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>고려 시대의 모든 기록 유산을 완료했습니다.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>badge_goryeo.png</t>
         </is>
       </c>
     </row>
@@ -5715,12 +5725,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>조선 기록 전문가</t>
+          <t>조선 컬렉터</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>조선 시대의 모든 기록 유산을 완료했습니다.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>badge_joseon.png</t>
         </is>
       </c>
     </row>
@@ -5742,12 +5757,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>근현대 기록 전문가</t>
+          <t>근현대 컬렉터</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>근현대의 모든 기록 유산을 완료했습니다.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>badge_modern.png</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5789,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>한국 기록 수호자</t>
+          <t>올 컴플리트</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>모든 시대의 기록 유산을 완료했습니다! 당신은 진정한 기록 수호자입니다.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>badge_allcomplete.png</t>
         </is>
       </c>
     </row>

--- a/content/기록문화_중등_콘텐츠.xlsx
+++ b/content/기록문화_중등_콘텐츠.xlsx
@@ -5698,7 +5698,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>고려 시대의 모든 기록 유산을 완료했습니다.</t>
+          <t>고려 시대의 기록 유산을 모두 수집했습니다! 고려의 기록을 끝까지 지켜낸 컬렉터예요.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>조선 시대의 모든 기록 유산을 완료했습니다.</t>
+          <t>조선 시대의 기록 유산을 모두 수집했습니다! 조선 왕조의 기록을 빠짐없이 모았어요.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>근현대의 모든 기록 유산을 완료했습니다.</t>
+          <t>근현대의 기록 유산을 모두 수집했습니다! 격동의 시대를 담은 기록을 지켜냈어요.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>모든 시대의 기록 유산을 완료했습니다! 당신은 진정한 기록 수호자입니다.</t>
+          <t>고려·조선·근현대, 모든 시대의 기록을 완성했습니다! 흩어진 기록을 전부 구해낸 최고의 기록 수호자예요.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">

--- a/content/기록문화_중등_콘텐츠.xlsx
+++ b/content/기록문화_중등_콘텐츠.xlsx
@@ -5496,7 +5496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5520,6 +5520,11 @@
           <t>icon</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>icon_b</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -5538,6 +5543,11 @@
           <t>level1.png</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>level1b.png</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -5556,6 +5566,11 @@
           <t>level2.png</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>level2b.png</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -5574,6 +5589,11 @@
           <t>level3.png</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>level3b.png</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -5592,6 +5612,11 @@
           <t>level4.png</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>level4b.png</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -5610,6 +5635,11 @@
           <t>level5.png</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>level5b.png</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -5626,6 +5656,11 @@
       <c r="D7" t="inlineStr">
         <is>
           <t>level6.png</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>level6b.png</t>
         </is>
       </c>
     </row>

--- a/content/기록문화_중등_콘텐츠.xlsx
+++ b/content/기록문화_중등_콘텐츠.xlsx
@@ -840,7 +840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -930,6 +930,11 @@
           <t>image_note</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="n">
@@ -994,6 +999,11 @@
           <t>해인사 대장경판(목판)</t>
         </is>
       </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>사진: 해인사 대장경판 ⓒSteve46814, CC BY-SA 3.0 (Wikimedia Commons)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="n">
@@ -1058,6 +1068,11 @@
           <t>원본 소장 프랑스국립도서관(BnF)</t>
         </is>
       </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>사진: 직지심체요절, 퍼블릭도메인/CC0 (Wikimedia Commons) · 원본 소장 프랑스국립도서관(BnF)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="n">
@@ -1122,6 +1137,11 @@
           <t>태백산사고본</t>
         </is>
       </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>사진: 조선왕조실록(태백산사고본), 국가유산청 · 공공누리 제1유형</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
@@ -1186,6 +1206,11 @@
           <t>국보 / 원본 소장 간송미술문화재단</t>
         </is>
       </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>사진: 훈민정음 해례본, 퍼블릭도메인 (Wikimedia Commons) · 원본 소장 간송미술문화재단</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
@@ -1250,6 +1275,11 @@
           <t>임진장초</t>
         </is>
       </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>사진: 난중일기, 국가유산청 · 퍼블릭도메인 (Wikimedia Commons)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
@@ -1314,6 +1344,11 @@
           <t>동의보감 본문(신형장부도)</t>
         </is>
       </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>사진: 동의보감 ⓒUlrich Lange, CC BY 4.0 (Wikimedia Commons)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
@@ -1378,6 +1413,11 @@
           <t>국채보상운동 기록물 전시</t>
         </is>
       </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>사진: 국채보상운동 기록물, CC BY 4.0 (Wikimedia Commons)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
@@ -1442,6 +1482,11 @@
           <t>형무소에서 보내 온 엽서</t>
         </is>
       </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>사진: 제주4·3 기록물(형무소에서 보내 온 엽서), 국가유산청 유네스코 세계기록유산</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
@@ -1506,6 +1551,11 @@
           <t>1960 가두시위 / 원소장처·이용허락 확인 필요</t>
         </is>
       </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>사진: 4·19혁명 기록물, 출처: 유네스코한국위원회(UNESCO 세계기록유산 소개)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
@@ -1570,6 +1620,11 @@
           <t>영일지구 사방사업 전후 / 이용허락 확인 권장</t>
         </is>
       </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>사진: 산림녹화 기록물 — 영일지구 사방사업, ⓒKorea Society of Forest Policy · UNESCO 세계기록유산</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
@@ -1634,6 +1689,11 @@
           <t>시민 기록 문서 / 이용허락 확인 필요</t>
         </is>
       </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>사진: 5·18 민주화운동 기록물, 출처: UNESCO 국제기록유산센터 · ⓒ국가기록원·광주광역시·5·18기념재단</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
@@ -1698,6 +1758,11 @@
           <t>이산가족 기록물 모음 / 이용범위 확인 필요</t>
         </is>
       </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>사진: KBS 특별생방송 '이산가족을 찾습니다' 기록물 ⓒ한국방송공사(KBS) · KBS 아카이브</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="n">
@@ -1762,6 +1827,11 @@
           <t>승정원일기 보물 제303호</t>
         </is>
       </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>사진: 승정원일기, 국가유산청 · 공공누리 제1유형 (Wikimedia Commons)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="n">
@@ -1824,6 +1894,11 @@
       <c r="N15" s="9" t="inlineStr">
         <is>
           <t>원행을묘정리의궤 처용무 정재 도설</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>사진: 조선왕조의궤(원행을묘정리의궤), 규장각한국학연구원 · 퍼블릭도메인 (Wikimedia Commons)</t>
         </is>
       </c>
     </row>

--- a/content/기록문화_중등_콘텐츠.xlsx
+++ b/content/기록문화_중등_콘텐츠.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="levels" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="badges" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sections" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="labels" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6037,4 +6038,66 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>connectionTitle</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>추가 정보</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>codePrompt</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>코드를 입력하세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>codeSubmit</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/content/기록문화_중등_콘텐츠.xlsx
+++ b/content/기록문화_중등_콘텐츠.xlsx
@@ -6046,7 +6046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6097,6 +6097,114 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>toastSave</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>기록 저장 성공!</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>completeTitle</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>기록 완성!</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>completeMeta</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>{country} · UNESCO {year}년 등재</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>completeSourceFallback</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>사진 출처 확인 중</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>levelUpNext</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>축하합니다! 다음은 '{next}'에 도전하세요!</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>levelUpMax</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>축하합니다! 최고 등급에 도달했어요!</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>badgeLocked</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>아직 획득하지 못한 배지예요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>codeWrong</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>코드가 틀렸습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>codeIncomplete</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>3자리를 모두 입력하세요.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content/기록문화_중등_콘텐츠.xlsx
+++ b/content/기록문화_중등_콘텐츠.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="badges" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sections" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="labels" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="quizzes" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6046,7 +6047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6205,6 +6206,498 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>quizTitle</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>배지 획득 퀴즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>quizGuide</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>타임라인에서 해당 기록유산을 다시 확인한 뒤 도전하세요!</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>era</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>question</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>opt1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>opt2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>opt3</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>opt4</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>고려</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>photo</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>사진을 보고 이 기록유산의 이름을 맞혀보세요.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>해인사 대장경판</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>직지심체요절</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>훈민정음 해례본</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>조선왕조실록</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>고려</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>직지심체요절의 세계사적 의의로 가장 알맞은 것은?</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>독일 구텐베르크의 금속활자보다 78년 앞선, 현존 세계 最古의 금속활자 인쇄본이다</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>세계 최초의 목판 인쇄물이다</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>한글을 처음으로 사용해 펴낸 책이다</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>세계에서 가장 먼저 종이를 발명한 기록이다</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>고려</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>해인사 대장경판이 오랜 세월 온전히 보존될 수 있었던 핵심 요인은?</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>장경판전이 자연 통풍으로 온도·습도를 스스로 조절하도록 설계되어서</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>경판을 진공 상태로 밀봉해 보관해서</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>매년 화학 약품으로 표면을 새로 코팅해서</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>지하 깊은 곳에 격리해 빛을 완전히 차단해서</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>조선</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>photo</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>사진을 보고 이 기록유산의 이름을 맞혀보세요.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>훈민정음 해례본</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>조선왕조실록</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>난중일기</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>동의보감</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>조선</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>조선왕조실록이 기록의 객관성을 지키기 위해 둔 장치로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>사관이 쓴 사초는 임금조차 볼 수 없도록 하였다</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>실록을 왕이 살아 있는 동안 직접 검토해 고쳤다</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>모든 기록을 한 곳에만 보관해 통제했다</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>외국 사신이 내용을 감수하도록 했다</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>조선</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>승정원일기에 대한 설명으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>승정원이 288년간 매일 국정을 적은, 현존 세계 최대 분량의 단일 역사 기록물이다</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>이순신이 전쟁 중에 쓴 친필 일기다</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>세종이 한글 창제 원리를 풀이한 책이다</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>왕실 행사를 그림으로 남긴 기록이다</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>근현대</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>photo</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>사진을 보고 이 기록유산의 이름을 맞혀보세요.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>KBS 이산가족을 찾습니다</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>4·19혁명 기록물</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>5·18 민주화운동 기록물</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>국채보상운동 기록물</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>근현대</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>국채보상운동의 역사적 의의로 가장 알맞은 것은?</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>국가 위기 때 시민이 자발적으로 나랏빚 상환에 나선, 세계사적으로 드문 시민 주도 모금 운동으로 훗날 IMF '금 모으기 운동'으로 이어졌다</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>정부가 세금을 걷어 나라 빚을 갚은 정책이다</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>일본이 한국의 빚을 대신 갚아 준 사건이다</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>외국 자본을 끌어들이기 위한 무역 운동이다</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>근현대</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>유네스코가 5·18민주화운동 기록물을 높이 평가한 이유로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>아시아 여러 나라의 민주화운동에 영향을 준, 국가폭력에 맞선 시민 저항의 종합 기록이라서</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>세계 최초의 금속활자로 인쇄된 기록이라서</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>왕실 행사를 그림으로 남긴 기록이라서</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>전쟁 중 장군이 직접 쓴 일기라서</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content/기록문화_중등_콘텐츠.xlsx
+++ b/content/기록문화_중등_콘텐츠.xlsx
@@ -6241,7 +6241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6322,26 +6322,26 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>조선왕조실록</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>해인사 대장경판</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>직지심체요절</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>훈민정음 해례본</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>조선왕조실록</t>
-        </is>
-      </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -6365,26 +6365,26 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>세계 최초의 목판 인쇄물이다</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>한글을 처음으로 사용해 펴낸 책이다</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>세계에서 가장 먼저 종이를 발명한 기록이다</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>독일 구텐베르크의 금속활자보다 78년 앞선, 현존 세계 最古의 금속활자 인쇄본이다</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>세계 최초의 목판 인쇄물이다</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>한글을 처음으로 사용해 펴낸 책이다</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>세계에서 가장 먼저 종이를 발명한 기록이다</t>
-        </is>
-      </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -6456,26 +6456,26 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>난중일기</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>동의보감</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>훈민정음 해례본</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>조선왕조실록</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>난중일기</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>동의보감</t>
-        </is>
-      </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -6499,26 +6499,26 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>외국 사신이 내용을 감수하도록 했다</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>사관이 쓴 사초는 임금조차 볼 수 없도록 하였다</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>실록을 왕이 살아 있는 동안 직접 검토해 고쳤다</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>모든 기록을 한 곳에만 보관해 통제했다</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>외국 사신이 내용을 감수하도록 했다</t>
-        </is>
-      </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -6542,26 +6542,26 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>이순신이 전쟁 중에 쓴 친필 일기다</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>세종이 한글 창제 원리를 풀이한 책이다</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>왕실 행사를 그림으로 남긴 기록이다</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>승정원이 288년간 매일 국정을 적은, 현존 세계 최대 분량의 단일 역사 기록물이다</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>이순신이 전쟁 중에 쓴 친필 일기다</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>세종이 한글 창제 원리를 풀이한 책이다</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>왕실 행사를 그림으로 남긴 기록이다</t>
-        </is>
-      </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -6633,26 +6633,26 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>일본이 한국의 빚을 대신 갚아 준 사건이다</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>외국 자본을 끌어들이기 위한 무역 운동이다</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>국가 위기 때 시민이 자발적으로 나랏빚 상환에 나선, 세계사적으로 드문 시민 주도 모금 운동으로 훗날 IMF '금 모으기 운동'으로 이어졌다</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>정부가 세금을 걷어 나라 빚을 갚은 정책이다</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>일본이 한국의 빚을 대신 갚아 준 사건이다</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>외국 자본을 끌어들이기 위한 무역 운동이다</t>
-        </is>
-      </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -6676,26 +6676,162 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>전쟁 중 장군이 직접 쓴 일기라서</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
           <t>아시아 여러 나라의 민주화운동에 영향을 준, 국가폭력에 맞선 시민 저항의 종합 기록이라서</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>세계 최초의 금속활자로 인쇄된 기록이라서</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>왕실 행사를 그림으로 남긴 기록이라서</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>전쟁 중 장군이 직접 쓴 일기라서</t>
-        </is>
-      </c>
       <c r="J10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>올컴플리트</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
         <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>photo</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>사진을 보고 이 기록유산의 이름을 맞혀보세요.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>조선왕조실록</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>동의보감</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>직지심체요절</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>난중일기</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>올컴플리트</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1907년, 담배를 끊어 마련한 돈을 보태는 등 신분과 성별을 가리지 않고 국민이 스스로 참여해 나라가 일본에 진 빚을 갚으려 한 운동의 기록유산은?</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>5·18 민주화운동 기록물</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>제주4·3 기록물</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>산림녹화 기록물</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>국채보상운동 기록물</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>올컴플리트</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>다음 기록유산을 만들어진 시기가 이른 것부터 바르게 나열한 것은?</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>제주4·3 기록물 → 산림녹화 기록물 → 해인사 대장경판</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>산림녹화 기록물 → 해인사 대장경판 → 제주4·3 기록물</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>해인사 대장경판 → 제주4·3 기록물 → 산림녹화 기록물</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>해인사 대장경판 → 산림녹화 기록물 → 제주4·3 기록물</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/content/기록문화_중등_콘텐츠.xlsx
+++ b/content/기록문화_중등_콘텐츠.xlsx
@@ -6047,7 +6047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6227,6 +6227,102 @@
       <c r="B15" t="inlineStr">
         <is>
           <t>타임라인에서 해당 기록유산을 다시 확인한 뒤 도전하세요!</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>endConfirmTitle</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>결과를 확인하시겠습니까?</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>endConfirmMsg</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>플레이 기록이 사라집니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>endConfirmYes</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>네</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>endConfirmNo</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>아니오</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>resultSecLevel</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>최종 레벨</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>resultSecBadges</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>최종 획득 배지</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>resultSecRecord</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>수집 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>resultSave</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>저장</t>
         </is>
       </c>
     </row>
@@ -6760,7 +6856,6 @@
           <t>text</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>1907년, 담배를 끊어 마련한 돈을 보태는 등 신분과 성별을 가리지 않고 국민이 스스로 참여해 나라가 일본에 진 빚을 갚으려 한 운동의 기록유산은?</t>
@@ -6804,7 +6899,6 @@
           <t>text</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>다음 기록유산을 만들어진 시기가 이른 것부터 바르게 나열한 것은?</t>

--- a/content/기록문화_중등_콘텐츠.xlsx
+++ b/content/기록문화_중등_콘텐츠.xlsx
@@ -15,6 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sections" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="labels" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="quizzes" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tutorial" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6047,7 +6048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6323,6 +6324,30 @@
       <c r="B23" t="inlineStr">
         <is>
           <t>저장</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>resultEmptyBadges</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>아직 획득한 배지가 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>resultEmptyRecords</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>아직 완성한 기록유산이 없어요.</t>
         </is>
       </c>
     </row>
@@ -6931,4 +6956,95 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>우리는 기록 수호대!</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>{name} {level} 환영합니다. 지금부터 우리는 여러 시대의 기록을 구하는 임무를 수행합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>흩어진 기록을 구하라!</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>우리의 소중한 기록 유산이 일부가 사라졌습니다. 사라진 기록을 찾아 숫자 코드를 입력하면 기록이 복원됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>시대의 배지를 모아라!</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>한 시대의 기록을 모두 복원하면 배지 퀴즈가 열립니다. 퀴즈를 통과해 시대 배지를 획득하세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>우리가 기록을 구한다!</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>{name} {level} 모든 준비가 끝났습니다. 지금 바로 기록을 구하러 출발하세요!</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>